--- a/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
@@ -203,7 +203,7 @@
     <t xml:space="preserve">e)  Kari vil skrive «vi skal være billigst i Oslo øst» som konkurransestrategi i punkt 1. Henger det sammen med situasjonsanalysen (punkt 2) og målene (punkt 3)? Bruk tallene. To setninger.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (overordnet strategi), 10.2 (situasjonsanalyse), 10.3 (markedsmål) og 10.4 (markedsstrategi, prispolitikk). Dekningsbidrag og dekningsgrad: Økonomistyring kap. 7. Elbilandel: Elbilforeningen, årsberetning 2025. Solkraft: NVE via pv magazine 13.01.2026. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (overordnet strategi), 10.2 (situasjonsanalyse), 10.3 (markedsmål) og 10.4 (markedsstrategi, prispolitikk). Dekningsbidrag og dekningsgrad: Økonomistyring 8.2. Elbilandel: Elbilforeningen, årsberetning 2025. Solkraft: NVE via pv magazine 13.01.2026. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>

--- a/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="165">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 10: Markedsplanen – et sammendrag (V5)</t>
   </si>
@@ -173,9 +173,18 @@
     <t xml:space="preserve">a)  Hvor mye ekstra dekningsbidrag gir delmålene i år, i kroner? Flere anlegg ganger 4 400 pluss flere ladepunkt ganger 1 050.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekstra DB = økning i antall × DB per enhet, summert over produktene (DB totalt = DB per enhet × M, Økonomistyring 8.2). Markedsmålene skal være tallfestede (Markedsføring 10.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor stor del av hver ny omsetningskrone blir dekningsbidrag? Ekstra dekningsbidrag delt på økt omsetning (4 055 570 − 3 335 640), i prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Dekningsgrad = DB × 100 / salgsinntekt (Økonomistyring 8.2, nr. 10), her brukt på økningen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Sorter de seks utsagnene i situasjonsanalysen. Er utsagnet en intern arbeidsbetingelse, altså en sterk eller svak side ved Nordlys selv? Svar ja eller nei for hvert.</t>
   </si>
   <si>
@@ -203,6 +212,24 @@
     <t xml:space="preserve">e)  Kari vil skrive «vi skal være billigst i Oslo øst» som konkurransestrategi i punkt 1. Henger det sammen med situasjonsanalysen (punkt 2) og målene (punkt 3)? Bruk tallene. To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Overordnet strategi (Markedsføring 10.1), situasjonsanalyse (10.2) og prispolitikk som kompromiss mellom kostnader, konkurrenter og betalingsvilje (10.4.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ekstra dekningsbidrag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regn bare økningen: 42 − 34 = 8 flere anlegg à 4 400 kr, og 215 − 180 = 35 flere ladepunkt à 1 050 kr. Del summen på økningen i omsetning, 4 055 570 − 3 335 640.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internt eller eksternt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hvert utsagn: rår Nordlys over dette selv (kompetanse, organisering, egen markedsføring), eller skjer det i markedet (trender, etterspørsel, konkurrenter)?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (overordnet strategi), 10.2 (situasjonsanalyse), 10.3 (markedsmål) og 10.4 (markedsstrategi, prispolitikk). Dekningsbidrag og dekningsgrad: Økonomistyring 8.2. Elbilandel: Elbilforeningen, årsberetning 2025. Solkraft: NVE via pv magazine 13.01.2026. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -266,18 +293,42 @@
     <t xml:space="preserve">a)  Hvor mange sikringsskapbytter er det i året i segmentet eneboliger bygd før 1980? Antall eneboliger × andel bygd før 1980 × andel som bytter.</t>
   </si>
   <si>
+    <t xml:space="preserve">Segmentets størrelse = antall i segmentet × andel som kjøper i året. Størrelse er det første kravet til en målgruppe (Markedsføring 10.4.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor stor markedsandel i segmentet krever Monas mål på 30 skapbytter? I prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Markedsandel = egen mengde / markedets mengde × 100 (markedsmål, Markedsføring kap. 3 og 10.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mye dekningsbidrag gir målet på 30 skapbytter i året, i kroner?</t>
   </si>
   <si>
+    <t xml:space="preserve">Samlet DB = DB per jobb × antall (Økonomistyring 8.2). Ressurskrav = timer per jobb × antall.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona retter all markedsføringen mot eneboligeiere med hus bygd før 1980, og tar andre jobber når de kommer. Hvilken markedsføringsform er det etter boka?   A: Udifferensiert, fordi alle i gruppen får samme tilbud   B: Konsentrert, fordi hun satser på én bestemt kundegruppe   C: Differensiert, fordi eneboliger før 1980 er et eget segment   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Oppfyller segmentet bokas tre krav til en målgruppe (størrelse, tilgjengelighet, identifiserbarhet)? Er målet realistisk? Skriv til slutt markedsmålet slik det skal stå i planen. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Krav til målgruppe: størrelse, tilgjengelighet og identifiserbarhet (Markedsføring 10.4.1). Krav til markedsmål: realistisk, tallfestet, i samsvar, hierarkisk og knyttet til tidspunkt (10.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Segmentet i antall jobber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 000 × 0,45 gir de eldre eneboligene. Gang med 0,05 for å få skapbytter i året. Del målet på 30 på det tallet for å få markedsandelen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hvor mange grupper?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Udifferensiert: samme tilbud til hele markedet. Differensiert: egne tilbud til flere målgrupper. Konsentrert: én bestemt gruppe. Hvor mange grupper retter Mona seg mot?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (udifferensiert, differensiert og konsentrert markedsføring), 10.3 (markedsmål) og 10.4.1 (segmentering og målgruppevalg). Segmenttallene er fra MA05, dekningsbidraget per sikringsskapbytte fra OK07. Fjell Elektro AS er en konstruert casebedrift; segmenttallene for Oslo øst er konstruerte.</t>
   </si>
   <si>
@@ -341,18 +392,42 @@
     <t xml:space="preserve">a)  Hva er budsjettsummen for handlingsplanen, i hele kroner? Legg sammen administrasjonstimene og montørtimene, gang med timesatsene, og legg til utleggene.</t>
   </si>
   <si>
+    <t xml:space="preserve">Budsjettpost = timer × timesats + utlegg; handlingsplanen har budsjett per linje (Markedsføring 10.5, tabell 10.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor stor del av det ekstra dekningsbidraget (71 950 kr) bruker handlingsplanen? I prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel = kostnad / gevinst × 100. Samme tankegang som nullpunktet (Økonomistyring 8.2): planen er en fast kostnad som DB skal dekke.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mye ekstra dekningsbidrag er igjen etter handlingsplanen hvis tre firedeler av delmålene nås? 0,75 × 71 950 minus budsjettsummen, i kroner.</t>
   </si>
   <si>
+    <t xml:space="preserve">Netto = andel av målet × ekstra DB − budsjettsum.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Milepælen i uke 12 er at alle ti styrebesøk er gjort. Bare fire er gjort. Kari sier: «Det tar vi i sluttevalueringen i uke 26.» Har hun rett etter boka?   A: Ja, evalueringen hører til når perioden er over   B: Nei, milepælene skal vise om bedriften er i rute mens det er tid til å justere   C: Nei, hele handlingsplanen må skrives om fra begynnelsen   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Styret vil kutte oppstartsmøtet (8 960 kr) og underveisevalueringen i uke 12 (4 timer, 1 310 kr) for å spare 10 270 kr. Hva svarer Kari? Bruk begreper fra kapitlet. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Gjennomføring med tilstrekkelige ressurser (Markedsføring 10.6), milepæler (10.7) og intern markedsføring (9.13).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budsjettsummen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legg sammen alle adm.timene (78) og gang med 327,43. Legg til 14 × 640 for oppstartsmøtet og utleggene 1 900 + 4 000.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bærer den seg?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Del budsjettsummen på 71 950 for andelen. Ved 75 % av målene: 0,75 × 71 950, minus budsjettsummen.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.5 med tabell 10.1 (handlingsplan med budsjett), 10.6 (gjennomføring, ressurser) og 10.7 (milepæler, evaluering). Vårkampanjen og timesatsene er de samme som i kap. 9 og appen. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -389,12 +464,21 @@
     <t xml:space="preserve">a)  Hva er budsjettsummen for handlingsplanen, i kroner? Egne timer × 590 kr pluss utleggene.</t>
   </si>
   <si>
+    <t xml:space="preserve">Budsjettpost = timer × timekostnad + utlegg (Markedsføring 10.5, tabell 10.1; timekostnad fra Økonomistyring kap. 5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange sikringsskapbytter à 3 000 kr i dekningsbidrag må planen gi før dekningsbidraget dekker budsjettsummen? Rund opp til helt tall.</t>
   </si>
   <si>
+    <t xml:space="preserve">Antall jobber = budsjettsum / DB per jobb, rundet opp (samme tankegang som nullpunkt i mengde, Økonomistyring 8.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hva koster markedsføringen per skapbytte hvis målet på 30 bytter nås? Budsjettsummen delt på 30, i hele kroner.</t>
   </si>
   <si>
+    <t xml:space="preserve">Markedsføringskostnad per jobb = budsjettsum / antall jobber.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona har skrevet seks utsagn i utkastet til handlingsplan. Hører hvert av dem hjemme i en handlingsplan (uke, aktivitet, mål, budsjett, ansvarlig)? Svar ja eller nei.</t>
   </si>
   <si>
@@ -417,6 +501,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Det er uke 12. Fire skap er byttet; milepælen var ti. Brevet har gitt 14 henvendelser, kvartsiden i avisa én. Hva gjør Mona nå? Bruk begreper fra kapitlet. To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strategien ligger fast, taktikken kan endres (Markedsføring 10.6); milepæler og fire spørsmål når målene ikke nås (10.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summen og jobbene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egne timer: 8 + 3 + 2 + 3, ganger 590 kr. Legg til utleggene. Del summen på 3 000 kr og rund opp for antall skapbytter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hører det hjemme?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En linje i handlingsplanen har uke, aktivitet, mål, budsjett og ansvarlig. Mangler den alt dette, er det et ønske, et mål eller en strategi.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.5 med tabell 10.1 (handlingsplan), 10.6 (strategien ligger fast, taktikken kan endres) og 10.7 (milepæler, fire spørsmål når målene ikke nås). Timekostnaden 590 kr er fra OK05, dekningsbidraget fra OK07. Fjell Elektro AS er en konstruert casebedrift; segmenttallene for Oslo øst er konstruerte.</t>
@@ -430,7 +529,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,8 +596,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,13 +635,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -573,7 +712,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -642,11 +781,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -687,8 +846,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -702,7 +861,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -716,7 +875,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1019,7 +1178,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1180,30 +1339,20 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(ABS(F21-(10))&lt;=0.05,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+      <c r="B21" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
         <v>51</v>
       </c>
@@ -1211,174 +1360,266 @@
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
+      <c r="F23" s="15"/>
       <c r="G23" s="16" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F23="","",IF(ABS(F23-(10))&lt;=0.05,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="16" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="17"/>
+      <c r="F27" s="19"/>
       <c r="G27" s="16" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="17"/>
+      <c r="F28" s="19"/>
       <c r="G28" s="16" t="str">
         <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
-      <c r="F29" s="17"/>
+      <c r="F29" s="19"/>
       <c r="G29" s="16" t="str">
-        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18"/>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-    </row>
-    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="F30" s="19"/>
+      <c r="G30" s="16" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="16" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="16" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="16" t="str">
+        <f aca="false">IF(F33="","",IF(UPPER(TRIM(F33))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+    </row>
+    <row r="45" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A17:G17"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B21:G21"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="B24:G24"/>
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A31:G33"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1395,7 +1636,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1406,7 +1647,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1416,7 +1657,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1427,7 +1668,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1441,63 +1682,63 @@
         <v>24</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1528,7 +1769,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1540,78 +1781,67 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(33.3))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(90000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(33.3))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
+    <row r="22" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(90000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>93</v>
+      </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
@@ -1619,41 +1849,148 @@
       <c r="G25" s="18"/>
     </row>
     <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+      <c r="A27" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1670,7 +2007,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1681,7 +2018,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1691,7 +2028,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1702,7 +2039,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1713,89 +2050,89 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="C8" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C9" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="19" t="n">
+        <v>113</v>
+      </c>
+      <c r="C10" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="20" t="n">
+        <v>115</v>
+      </c>
+      <c r="C11" s="25" t="n">
         <v>1900</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="19" t="n">
+        <v>109</v>
+      </c>
+      <c r="C12" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C13" s="20" t="n">
+        <v>118</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="C14" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1827,7 +2164,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1839,120 +2176,216 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(56.1))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(13563))&lt;=2,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="17"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="16" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(56.1))&lt;=0.1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="18"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18"/>
-      <c r="B25" s="18"/>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="16" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(13563))&lt;=2,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>126</v>
+      </c>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
       <c r="E25" s="18"/>
       <c r="F25" s="18"/>
       <c r="G25" s="18"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="16" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="20"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23"/>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="23"/>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1969,7 +2402,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1980,7 +2413,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1990,7 +2423,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2001,7 +2434,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2012,83 +2445,83 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="19" t="n">
+        <v>138</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="B9" s="13"/>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="25" t="n">
         <v>14400</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B10" s="11"/>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="24" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B11" s="13"/>
-      <c r="C11" s="20" t="n">
+      <c r="C11" s="25" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B12" s="19" t="n">
+        <v>142</v>
+      </c>
+      <c r="B12" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="B13" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="20" t="n">
+      <c r="C13" s="25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B14" s="19" t="n">
+        <v>144</v>
+      </c>
+      <c r="B14" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2120,7 +2553,7 @@
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2132,205 +2565,301 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="16" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(13))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="16" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(1261))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="16" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="NEI","Riktig","Prøv igjen"))</f>
+      <c r="F21" s="15"/>
+      <c r="G21" s="16" t="str">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(13))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="16" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C22" s="18"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="17"/>
+      <c r="F24" s="15"/>
       <c r="G24" s="16" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F24="","",IF(ABS(F24-(1261))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="16" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="16" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+    </row>
+    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="16" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="33" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="16" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="16" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="16" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="16" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="16" t="str">
+        <f aca="false">IF(F32="","",IF(UPPER(TRIM(F32))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="7"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="16" t="str">
+        <f aca="false">IF(F33="","",IF(UPPER(TRIM(F33))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="20"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="20"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="20"/>
+      <c r="B37" s="20"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="B42" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="23"/>
+    </row>
+    <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
+      <c r="G43" s="23"/>
+    </row>
+    <row r="45" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="B25:G25"/>
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A35:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Markedsplanen har sju punkt i fast rekkefølge (10.1–10.7). Punkt 2, situasjonsanalysen, kartlegger interne arbeidsbetingelser (sterke og svake sider) og eksterne (muligheter og trusler). Punkt 3, markedsmålene, skal være realistiske, tallfestede, innbyrdes i samsvar og hierarkiske. Regn målene om til dekningsbidrag: det er det som skal betale tiltakene i handlingsplanen. Punkt 4 og den overordnede strategien i punkt 1 må passe med situasjonsanalysen: differensiert markedsføring (egne tilbud til ulike målgrupper) er noe annet enn Porters differensiering, og prisen er alltid et kompromiss mellom kostnader, konkurrenter og betalingsvilje.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle- og ladeavdelingen i Nordlys monterte 34 solcelleanlegg (51 360 kr, 4 400 kr i dekningsbidrag per anlegg) og 180 ladepunkt (8 830 kr, 1 050 kr i dekningsbidrag) i fjor, og omsatte for 3 335 640 kr. Delmålene i år er 42 anlegg og 215 ladepunkt til samme priser, som gir 4 055 570 kr. Kari skal sette punkt 1–4 i markedsplanen sammen. Situasjonsanalysen har seks utsagn (S1–S6 i tabellen). Gå fram slik: regn det ekstra dekningsbidraget delmålene gir, regn hvor mye av hver ny omsetningskrone som blir dekningsbidrag, sorter utsagnene i internt og eksternt, og vurder til slutt om strategien henger sammen med analysen.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle- og ladeavdelingen i Nordlys monterte 34 solcelleanlegg (51 360 kr, 4 400 kr i dekningsbidrag per anlegg) og 180 ladepunkt (8 830 kr, 1 050 kr i dekningsbidrag) i fjor, og omsatte for 3 335 640 kr. Delmålene i år er 42 anlegg og 215 ladepunkt til samme priser, som gir 4 055 570 kr. Kari skal sette punkt 1–4 i markedsplanen sammen. Situasjonsanalysen har seks utsagn (utsagn 1–6 i tabellen). Gå fram slik: regn det ekstra dekningsbidraget delmålene gir, regn hvor mye av hver ny omsetningskrone som blir dekningsbidrag, sorter utsagnene i internt og eksternt, og vurder til slutt om strategien henger sammen med analysen.</t>
   </si>
   <si>
     <t xml:space="preserve">Fakta</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">Solcelleanlegg</t>
   </si>
   <si>
-    <t xml:space="preserve">34 i fjor, mål 42 · 51 360 kr · DB 4 400</t>
+    <t xml:space="preserve">34 i fjor, mål 42 · 51 360 kr · dekningsbidrag 4 400</t>
   </si>
   <si>
     <t xml:space="preserve">Ladepunkt</t>
   </si>
   <si>
-    <t xml:space="preserve">180 i fjor, mål 215 · 8 830 kr · DB 1 050</t>
+    <t xml:space="preserve">180 i fjor, mål 215 · 8 830 kr · dekningsbidrag 1 050</t>
   </si>
   <si>
     <t xml:space="preserve">Omsetning</t>
@@ -122,37 +122,37 @@
     <t xml:space="preserve">3 335 640 i fjor · mål 4 055 570</t>
   </si>
   <si>
-    <t xml:space="preserve">S1</t>
+    <t xml:space="preserve">Utsagn 1</t>
   </si>
   <si>
     <t xml:space="preserve">Avdelingen har ingen egen leder</t>
   </si>
   <si>
-    <t xml:space="preserve">S2</t>
+    <t xml:space="preserve">Utsagn 2</t>
   </si>
   <si>
     <t xml:space="preserve">Nordlys har aldri kjøpt en annonse</t>
   </si>
   <si>
-    <t xml:space="preserve">S3</t>
+    <t xml:space="preserve">Utsagn 3</t>
   </si>
   <si>
     <t xml:space="preserve">32,5 % av personbilene er elbiler</t>
   </si>
   <si>
-    <t xml:space="preserve">S4</t>
+    <t xml:space="preserve">Utsagn 4</t>
   </si>
   <si>
     <t xml:space="preserve">Ny solkraft i Norge falt 21,5 % i 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">S5</t>
+    <t xml:space="preserve">Utsagn 5</t>
   </si>
   <si>
     <t xml:space="preserve">Landsdekkende kjeder i Oslo øst</t>
   </si>
   <si>
-    <t xml:space="preserve">S6</t>
+    <t xml:space="preserve">Utsagn 6</t>
   </si>
   <si>
     <t xml:space="preserve">12 montører; Kari er installatør</t>
@@ -176,34 +176,34 @@
     <t xml:space="preserve">Formel og begrep</t>
   </si>
   <si>
-    <t xml:space="preserve">Ekstra DB = økning i antall × DB per enhet, summert over produktene (DB totalt = DB per enhet × M, Økonomistyring 8.2). Markedsmålene skal være tallfestede (Markedsføring 10.3).</t>
+    <t xml:space="preserve">Ekstra dekningsbidrag = økning i antall × dekningsbidrag per enhet, summert over produktene (samlet dekningsbidrag = dekningsbidrag per enhet × mengde, Økonomistyring 8.2). Markedsmålene skal være tallfestede (Markedsføring 10.3).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hvor stor del av hver ny omsetningskrone blir dekningsbidrag? Ekstra dekningsbidrag delt på økt omsetning (4 055 570 − 3 335 640), i prosent med én desimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dekningsgrad = DB × 100 / salgsinntekt (Økonomistyring 8.2, nr. 10), her brukt på økningen.</t>
+    <t xml:space="preserve">Dekningsgrad = dekningsbidrag × 100 / salgsinntekt (Økonomistyring 8.2, nr. 10), her brukt på økningen.</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Sorter de seks utsagnene i situasjonsanalysen. Er utsagnet en intern arbeidsbetingelse, altså en sterk eller svak side ved Nordlys selv? Svar ja eller nei for hvert.</t>
   </si>
   <si>
-    <t xml:space="preserve">      S1 Avdelingen har ingen egen leder   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      S2 Nordlys har aldri kjøpt en annonse   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      S3 32,5 % av personbilene er elbiler   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      S4 Ny solkraft i Norge falt 21,5 % i 2025   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      S5 Landsdekkende kjeder i Oslo øst   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      S6 12 montører; Kari er installatør   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Utsagn 1: Avdelingen har ingen egen leder   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Utsagn 2: Nordlys har aldri kjøpt en annonse   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Utsagn 3: 32,5 % av personbilene er elbiler   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Utsagn 4: Ny solkraft i Norge falt 21,5 % i 2025   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Utsagn 5: Landsdekkende kjeder i Oslo øst   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Utsagn 6: 12 montører; Kari er installatør   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Avdelingen gir eneboligkunden et fastpristilbud gjennom en målrettet annonse, og borettslagsstyret befaring, kvantumsrabatt og et personlig besøk. Hva kaller boka dette?   A: Porters differensiering: høyere pris for en merverdi kunden ser   B: Differensiert markedsføring: egne tilbud til ulike målgrupper   C: Konsentrert markedsføring: satsing på én bestemt kundegruppe   (skriv bokstaven)</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">Spør for hvert utsagn: rår Nordlys over dette selv (kompetanse, organisering, egen markedsføring), eller skjer det i markedet (trender, etterspørsel, konkurrenter)?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (overordnet strategi), 10.2 (situasjonsanalyse), 10.3 (markedsmål) og 10.4 (markedsstrategi, prispolitikk). Dekningsbidrag og dekningsgrad: Økonomistyring 8.2. Elbilandel: Elbilforeningen, årsberetning 2025. Solkraft: NVE via pv magazine 13.01.2026. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (overordnet strategi), 10.2 (situasjonsanalyse), 10.3 (markedsmål) og 10.4 (markedsstrategi, prispolitikk). Dekningsbidrag og dekningsgrad: Økonomistyring 8.2. Elbilandel: Elbilforeningen, årsberetning 2025. Solkraft: Norges vassdrags- og energidirektorat (NVE) via pv magazine 13.01.2026. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">c)  Hvor mye dekningsbidrag gir målet på 30 skapbytter i året, i kroner?</t>
   </si>
   <si>
-    <t xml:space="preserve">Samlet DB = DB per jobb × antall (Økonomistyring 8.2). Ressurskrav = timer per jobb × antall.</t>
+    <t xml:space="preserve">Samlet dekningsbidrag = dekningsbidrag per jobb × antall (Økonomistyring 8.2). Ressurskrav = timer per jobb × antall.</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Mona retter all markedsføringen mot eneboligeiere med hus bygd før 1980, og tar andre jobber når de kommer. Hvilken markedsføringsform er det etter boka?   A: Udifferensiert, fordi alle i gruppen får samme tilbud   B: Konsentrert, fordi hun satser på én bestemt kundegruppe   C: Differensiert, fordi eneboliger før 1980 er et eget segment   (skriv bokstaven)</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">Udifferensiert: samme tilbud til hele markedet. Differensiert: egne tilbud til flere målgrupper. Konsentrert: én bestemt gruppe. Hvor mange grupper retter Mona seg mot?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (udifferensiert, differensiert og konsentrert markedsføring), 10.3 (markedsmål) og 10.4.1 (segmentering og målgruppevalg). Segmenttallene er fra MA05, dekningsbidraget per sikringsskapbytte fra OK07. Fjell Elektro AS er en konstruert casebedrift; segmenttallene for Oslo øst er konstruerte.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.1 (udifferensiert, differensiert og konsentrert markedsføring), 10.3 (markedsmål) og 10.4.1 (segmentering og målgruppevalg). Segmenttallene er fra Markedsføring kap. 5, dekningsbidraget per sikringsskapbytte fra Økonomistyring kap. 7. Fjell Elektro AS er en konstruert casebedrift; segmenttallene for Oslo øst er konstruerte.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: handlingsplanen for rammeavtalen, budsjett og evaluering</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">3 Idémyldring i ledermøtet</t>
   </si>
   <si>
-    <t xml:space="preserve">6 adm.</t>
+    <t xml:space="preserve">6 administrasjon</t>
   </si>
   <si>
     <t xml:space="preserve">4 Kartlegging av 24 borettslag</t>
   </si>
   <si>
-    <t xml:space="preserve">10 adm.</t>
+    <t xml:space="preserve">10 administrasjon</t>
   </si>
   <si>
     <t xml:space="preserve">5 Oppstartsmøte for alle 18</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">6 Brev til 24 styreledere</t>
   </si>
   <si>
-    <t xml:space="preserve">5 adm.</t>
+    <t xml:space="preserve">5 administrasjon</t>
   </si>
   <si>
     <t xml:space="preserve">7 Telefon til de 24</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">8–11 Ti styrebesøk</t>
   </si>
   <si>
-    <t xml:space="preserve">38,5 adm.</t>
+    <t xml:space="preserve">38,5 administrasjon</t>
   </si>
   <si>
     <t xml:space="preserve">12–26 Evaluering og signering</t>
   </si>
   <si>
-    <t xml:space="preserve">12,5 adm.</t>
+    <t xml:space="preserve">12,5 administrasjon</t>
   </si>
   <si>
     <t xml:space="preserve">a)  Hva er budsjettsummen for handlingsplanen, i hele kroner? Legg sammen administrasjonstimene og montørtimene, gang med timesatsene, og legg til utleggene.</t>
@@ -398,13 +398,13 @@
     <t xml:space="preserve">b)  Hvor stor del av det ekstra dekningsbidraget (71 950 kr) bruker handlingsplanen? I prosent med én desimal.</t>
   </si>
   <si>
-    <t xml:space="preserve">Andel = kostnad / gevinst × 100. Samme tankegang som nullpunktet (Økonomistyring 8.2): planen er en fast kostnad som DB skal dekke.</t>
+    <t xml:space="preserve">Andel = kostnad / gevinst × 100. Samme tankegang som nullpunktet (Økonomistyring 8.2): planen er en fast kostnad som dekningsbidraget skal dekke.</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Hvor mye ekstra dekningsbidrag er igjen etter handlingsplanen hvis tre firedeler av delmålene nås? 0,75 × 71 950 minus budsjettsummen, i kroner.</t>
   </si>
   <si>
-    <t xml:space="preserve">Netto = andel av målet × ekstra DB − budsjettsum.</t>
+    <t xml:space="preserve">Netto = andel av målet × ekstra dekningsbidrag − budsjettsum.</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Milepælen i uke 12 er at alle ti styrebesøk er gjort. Bare fire er gjort. Kari sier: «Det tar vi i sluttevalueringen i uke 26.» Har hun rett etter boka?   A: Ja, evalueringen hører til når perioden er over   B: Nei, milepælene skal vise om bedriften er i rute mens det er tid til å justere   C: Nei, hele handlingsplanen må skrives om fra begynnelsen   (skriv bokstaven)</t>
@@ -419,7 +419,7 @@
     <t xml:space="preserve">Budsjettsummen</t>
   </si>
   <si>
-    <t xml:space="preserve">Legg sammen alle adm.timene (78) og gang med 327,43. Legg til 14 × 640 for oppstartsmøtet og utleggene 1 900 + 4 000.</t>
+    <t xml:space="preserve">Legg sammen alle administrasjonstimene (78) og gang med 327,43. Legg til 14 × 640 for oppstartsmøtet og utleggene 1 900 + 4 000.</t>
   </si>
   <si>
     <t xml:space="preserve">Bærer den seg?</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">b)  Hvor mange sikringsskapbytter à 3 000 kr i dekningsbidrag må planen gi før dekningsbidraget dekker budsjettsummen? Rund opp til helt tall.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antall jobber = budsjettsum / DB per jobb, rundet opp (samme tankegang som nullpunkt i mengde, Økonomistyring 8.2).</t>
+    <t xml:space="preserve">Antall jobber = budsjettsum / dekningsbidrag per jobb, rundet opp (samme tankegang som nullpunkt i mengde, Økonomistyring 8.2).</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Hva koster markedsføringen per skapbytte hvis målet på 30 bytter nås? Budsjettsummen delt på 30, i hele kroner.</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">En linje i handlingsplanen har uke, aktivitet, mål, budsjett og ansvarlig. Mangler den alt dette, er det et ønske, et mål eller en strategi.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.5 med tabell 10.1 (handlingsplan), 10.6 (strategien ligger fast, taktikken kan endres) og 10.7 (milepæler, fire spørsmål når målene ikke nås). Timekostnaden 590 kr er fra OK05, dekningsbidraget fra OK07. Fjell Elektro AS er en konstruert casebedrift; segmenttallene for Oslo øst er konstruerte.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 10, avsnitt 10.5 med tabell 10.1 (handlingsplan), 10.6 (strategien ligger fast, taktikken kan endres) og 10.7 (milepæler, fire spørsmål når målene ikke nås). Timekostnaden 590 kr er fra Økonomistyring kap. 5, dekningsbidraget fra kap. 7. Fjell Elektro AS er en konstruert casebedrift; segmenttallene for Oslo øst er konstruerte.</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1227,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>26</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
         <v>28</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
         <v>49</v>
       </c>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
         <v>49</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="17" t="s">
         <v>49</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
         <v>110</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>117</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
         <v>119</v>
       </c>

--- a/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="165">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 10: Markedsplanen – et sammendrag (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 10: Markedsplanen – et sammendrag (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma10/MA10_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Markedsplanen har sju punkt i fast rekkefølge (10.1–10.7). Punkt 2, situasjonsanalysen, kartlegger interne arbeidsbetingelser (sterke og svake sider) og eksterne (muligheter og trusler). Punkt 3, markedsmålene, skal være realistiske, tallfestede, innbyrdes i samsvar og hierarkiske. Regn målene om til dekningsbidrag: det er det som skal betale tiltakene i handlingsplanen. Punkt 4 og den overordnede strategien i punkt 1 må passe med situasjonsanalysen: differensiert markedsføring (egne tilbud til ulike målgrupper) er noe annet enn Porters differensiering, og prisen er alltid et kompromiss mellom kostnader, konkurrenter og betalingsvilje.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle- og ladeavdelingen i Nordlys monterte 34 solcelleanlegg (51 360 kr, 4 400 kr i dekningsbidrag per anlegg) og 180 ladepunkt (8 830 kr, 1 050 kr i dekningsbidrag) i fjor, og omsatte for 3 335 640 kr. Delmålene i år er 42 anlegg og 215 ladepunkt til samme priser, som gir 4 055 570 kr. Kari skal sette punkt 1–4 i markedsplanen sammen. Situasjonsanalysen har seks utsagn (utsagn 1–6 i tabellen). Gå fram slik: regn det ekstra dekningsbidraget delmålene gir, regn hvor mye av hver ny omsetningskrone som blir dekningsbidrag, sorter utsagnene i internt og eksternt, og vurder til slutt om strategien henger sammen med analysen.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle- og ladeavdelingen i Nordlys monterte 34 solcelleanlegg (51 360 kr, 4 400 kr i dekningsbidrag per anlegg) og 180 ladepunkt (8 830 kr, 1 050 kr i dekningsbidrag) i fjor, og omsatte for 34 × 51 360 + 180 × 8 830 = 3 335 640 kr. Delmålene i år er 42 anlegg og 215 ladepunkt til samme priser, som gir 42 × 51 360 + 215 × 8 830 = 4 055 570 kr. Kari skal sette punkt 1–4 i markedsplanen sammen. Situasjonsanalysen har seks utsagn (utsagn 1–6 i tabellen). Gå fram slik: regn det ekstra dekningsbidraget delmålene gir, regn hvor mye av hver ny omsetningskrone som blir dekningsbidrag, sorter utsagnene i internt og eksternt, og vurder til slutt om strategien henger sammen med analysen.</t>
   </si>
   <si>
     <t xml:space="preserve">Fakta</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">180 i fjor, mål 215 · 8 830 kr · dekningsbidrag 1 050</t>
   </si>
   <si>
-    <t xml:space="preserve">Omsetning</t>
+    <t xml:space="preserve">Omsetning (antall × pris)</t>
   </si>
   <si>
     <t xml:space="preserve">3 335 640 i fjor · mål 4 055 570</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">Utsagn 3</t>
   </si>
   <si>
-    <t xml:space="preserve">32,5 % av personbilene er elbiler</t>
+    <t xml:space="preserve">32,5 % av personbilene er elbiler (Elbilforeningen)</t>
   </si>
   <si>
     <t xml:space="preserve">Utsagn 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Ny solkraft i Norge falt 21,5 % i 2025</t>
+    <t xml:space="preserve">Ny solkraft falt 21,5 % i 2025 (Norges vassdrags- og energidirektorat: 149 → 117 megawatt)</t>
   </si>
   <si>
     <t xml:space="preserve">Utsagn 5</t>
@@ -194,10 +194,10 @@
     <t xml:space="preserve">      Utsagn 2: Nordlys har aldri kjøpt en annonse   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      Utsagn 3: 32,5 % av personbilene er elbiler   (Ja eller Nei)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">      Utsagn 4: Ny solkraft i Norge falt 21,5 % i 2025   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Utsagn 3: 32,5 % av personbilene er elbiler (Elbilforeningen)   (Ja eller Nei)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Utsagn 4: Ny solkraft i Norge falt 21,5 % i 2025 (Norges vassdrags- og energidirektorat: fra 149 til 117 megawatt)   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Utsagn 5: Landsdekkende kjeder i Oslo øst   (Ja eller Nei)</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Kort oppsummert: Handlingsplanen er den kortsiktige iverksettelsen av strategien (10.5). Hver linje har uke, aktivitet, mål, budsjett og ansvarlig, og planen har en sum. Budsjettposten regnes av timer og utlegg: timer × timesats + utlegg. Sett summen opp mot det ekstra dekningsbidraget målene gir: da ser du hvor stor del av gevinsten planen bruker, og hva som er igjen hvis målene bare delvis nås. Milepæler underveis gjør at resultatet ikke kommer som en overraskelse (10.7).</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Delmål 1.3 i markedsplanen er en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni. Kari har satt opp handlingsplanen med ni linjer. Kjernen er vårkampanjen fra kapittel 9: brevet, oppstartsmøtet og ti styrebesøk. En administrasjonstime koster 327,43 kr og en montørtime 640 kr. Delmålene for året gir 71 950 kr i ekstra dekningsbidrag (A1). Gå fram slik: legg sammen timene og utleggene og regn budsjettsummen, regn hvor stor del av det ekstra dekningsbidraget planen bruker, regn hva som er igjen hvis tre firedeler av målene nås, og vurder milepælene og et forslag om å kutte.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Delmål 1.3 i markedsplanen er en rammeavtale med et borettslag om minst 20 ladepunkt innen 30. juni. Kari har satt opp handlingsplanen med ni linjer. Kjernen er vårkampanjen fra kapittel 9: brevet, oppstartsmøtet og ti styrebesøk. En administrasjonstime koster 327,43 kr (administrasjonens lønnskostnad 2 220 000 kr delt på 4 × 1 695 timer, faktaarket) og en montørtime 640 kr. Delmålene for året gir 71 950 kr i ekstra dekningsbidrag (A1). Gå fram slik: legg sammen timene og utleggene og regn budsjettsummen, regn hvor stor del av det ekstra dekningsbidraget planen bruker, regn hva som er igjen hvis tre firedeler av målene nås, og vurder milepælene og et forslag om å kutte.</t>
   </si>
   <si>
     <t xml:space="preserve">Uke og aktivitet</t>
@@ -1208,7 +1208,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>23</v>
       </c>
@@ -1267,7 +1267,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
         <v>36</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
         <v>38</v>
       </c>
@@ -1430,7 +1430,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
         <v>57</v>
       </c>
@@ -2037,7 +2037,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>104</v>
       </c>
